--- a/docs/BOM.xlsx
+++ b/docs/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Annie\code\hardware\IFLY-Drone\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B130839-ED3D-4CF0-9227-2C98A4282793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB0EA70-41A9-4BC9-BDE0-E87194DBE31C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{DB92A48D-E83D-46BB-8A38-716615493FA1}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{DB92A48D-E83D-46BB-8A38-716615493FA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Product name</t>
   </si>
@@ -75,6 +75,24 @@
   </si>
   <si>
     <t>F450 Frame</t>
+  </si>
+  <si>
+    <t>NRF2401 transceivers</t>
+  </si>
+  <si>
+    <t>4S 3300mAh Lipo Battery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery Charger </t>
+  </si>
+  <si>
+    <t>9450 Propellers</t>
+  </si>
+  <si>
+    <t>Arduino</t>
+  </si>
+  <si>
+    <t>ESP 32-CAM-MB</t>
   </si>
 </sst>
 </file>
@@ -450,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2011A3C7-6E29-4B04-A4B3-8D5C6DD982D4}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" customWidth="1"/>
@@ -525,6 +543,48 @@
         <v>48.29</v>
       </c>
     </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/BOM.xlsx
+++ b/docs/BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Annie\code\hardware\IFLY-Drone\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB0EA70-41A9-4BC9-BDE0-E87194DBE31C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC5C64E-7104-4BA1-9075-0AAC0485C5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{DB92A48D-E83D-46BB-8A38-716615493FA1}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>Product name</t>
   </si>
@@ -89,10 +89,64 @@
     <t>9450 Propellers</t>
   </si>
   <si>
-    <t>Arduino</t>
-  </si>
-  <si>
     <t>ESP 32-CAM-MB</t>
+  </si>
+  <si>
+    <t>Arduino (Leonardo)</t>
+  </si>
+  <si>
+    <t>Gikfun GY-521 MPU-6050 3 Axis Accelerometer Gyroscope Module</t>
+  </si>
+  <si>
+    <t>RC-Brushless 80A</t>
+  </si>
+  <si>
+    <t>HAWK’S WORK F450 Drone Frame</t>
+  </si>
+  <si>
+    <t>Sunnysky 2212 980kv brushless motors</t>
+  </si>
+  <si>
+    <t>DJI Phantom 8Pcs/Set Self-Locking Quadcopter Blades - 4 x 9450 CW + 4 x 9450 CCW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pishop.ca/product/raspberry-pi-pico-non-wireless/?src=raspberrypi  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gikfun GY-521 MPU-6050 3 Axis Accelerometer Gyroscope Module 6 DOF 6-axis Accelerometer Gyroscope Sensor Module for Arduino DIY(Pack of 3) EK1091x3C </t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/RC-Brushless-Electric-Controller-bullet/dp/B071GRSFBD?th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/HAWKS-WORK-Quadcopter-Original-version/dp/B09YQ4G4ZZ?source=ps-sl-shoppingads-lpcontext&amp;ref_=fplfs&amp;smid=A2Z91JXWPM95ID&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ca/dp/B0CGRK4PZ9/ref=twister_B0DG61WS8R?_encoding=UTF8&amp;th=1 </t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/diymore-NRF24L01-Transceiver-Development-Compatible/dp/B0CGTWQ1BP/ref=sr_1_2?crid=N7UCP8G6BI4B&amp;dib=eyJ2IjoiMSJ9.QZWyUbxu-TTSXPtYa6jWsruNzInPMMFV3gyAWClyr16MjHZf7YNdMQIuLN8GSAJLMNuq_XRXSs0m0G5N2sjBIhiwK3Z4KvY9esEi6FYL8DDdseyeCPcQ7UDiiZB5kaqveZb2Wb01HFBp9DZ7mam3NE9XG7xw6UoxfQr9Gs2KcmLq1bCmSb6KFCsLg2RbVpZ_.s2cC8epe2nNatPfmenG33v9DyfE5sOt-iBPax3x-Jwg&amp;dib_tag=se&amp;keywords=nrf2401%2Bpa%2Blna&amp;qid=1729738278&amp;sprefix=nrf2401%2Bpa%2Blna%2Caps%2C100&amp;sr=8-2&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/3300mAh-Battery-Helicopter-Airplane-Quadcopter/dp/B06XKQJZ8D/ref=sr_1_3_sspa?crid=25ULWJT7C7R66&amp;dib=eyJ2IjoiMSJ9.vYiAFw8wx-yRT8mrrvJ9F8iDFepM-goQbSaENXXv1p29dstKtQIYZaj1pn7rGGAGnxdMgoLHrOMQY91OKu51v8WLdjkq4eCi5EKe8z_K4cxcPbNP13Z1RKbgGnhs872aFBYGAh5eJIDjqL14oiAvwBw3eysdwf1lhxGnkO44qkwR113S583LExSDaa1urb2P0Y3cqxNoYUGVdBMDAMReQhU-SncWWSIWO4WEub3ZmS-SjueGbxuDC_AJcCAtAgLVxzIGmlzZL8pKUVzUuEKxSRbdivPCv_PMbDSxuVM6sK4.MMM72QgdE4MEe_CbP1cIRc1AZmN33Ov_NqM5hDzDp8A&amp;dib_tag=se&amp;keywords=4s+lipo+3000mah&amp;qid=1729985037&amp;sprefix=4S+LiPo+3%2Caps%2C81&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t>https://sunnyskyusa.com/products/sunnysky-a2212-motors-multirotor-version?srsltid=AfmBOoppH0aekND_UVhPL1lqfTTU9KIqaeMy3LDPvhpOP_b6vSqr5xUa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ca/Leonardo-Headers-Compatible-Revision-Atmega32u4/dp/B00R237VGO/ref=sr_1_5?crid=MC17YS7O9GW9&amp;dib=eyJ2IjoiMSJ9.JMDO9D4vLSrBk_dqVlo-qYpD2emjzeRNG8QL6R8lWGXJUfLWeuU9lkv-AmMXoQJtSdgf6mjRUevYifaj76GKPczdq8-ZPujBm9azFK_jRVBBBxGQ1Iq-UgO_xESHbJL8yc7U0JgTmjihDuHQlgqb1gUqg-HUfgTJJeGmwypsadu_ivg6lFpJP9DrDnsP7rn8GIOX4dFpL6QSGQzulkHG-m7jKz6eSMoNHKHwlVnIjqLFz1WFLYKdxypg1TMg-ZzYmxVo8vHP00SBqcrwLuKwlAzuV_xVFZb3HXRtRz_V0YE.odwVut84lRl1xHouDFEbRF0YtTtdC_Kp_PjlXUqnVfU&amp;dib_tag=se&amp;keywords=arduino+leonardo&amp;qid=1730080008&amp;s=electronics&amp;sprefix=arduino+leonardo%2Celectronics%2C117&amp;sr=1-5 </t>
+  </si>
+  <si>
+    <t>https://www.amazon.ca/Hobby-Fans-Professional-Balance-Discharger/dp/B09XC91BWJ/ref=sr_1_4_sspa?crid=38YSB72VYU6CH&amp;dib=eyJ2IjoiMSJ9.lnM2r6NhD8BJ0diYESu45Q1KQVNPU83hWGmkyM0idZS5APeLiSXCExN5IKIisgJh44yVmbwwP0E7zlbheFz3jKk_iwooFuWlrKiEnSXo5z2Hm1XyjvWMUTACgwu-K6noYPaE1KPmuIRgNc3VBkO0cb2wYWJEtMmLF4PDafVH0bSmUMwI1RbRu4_uRscwDZ7bZEq_wFA83RKeft44gD9qEySyDZEvFfr87CBL2GZFTJcoBO3JMDktAZ_sv86Svj0N_moTYnS4xrkUQI3MXR_SK9aKKv6LZfIlxSP2LDkF9Mw.o5z9RHJirvUDYHafc2uyBP8i3uW1x5a_-s5JsqYVZDc&amp;dib_tag=se&amp;keywords=lipo+battery+charger&amp;qid=1730085173&amp;sprefix=lipo+battery%2Caps%2C103&amp;sr=8-4-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/32844447546.html?spm=a2g0o.productlist.main.3.4f2b2e3fBpldJr&amp;algo_pvid=b55a8f97-69bd-4069-bb1c-8dd3c90e7c96&amp;algo_exp_id=b55a8f97-69bd-4069-bb1c-8dd3c90e7c96-1&amp;pdp_npi=4%40dis%21CAD%2113.62%2112.91%21%21%219.61%219.11%21%402101e9a217299675201923501e356e%2166150463925%21sea%21CA%210%21ABX&amp;curPageLogUid=nGstg93h37eM&amp;utparam-url=scene%3Asearch%7Cquery_from%3A</t>
+  </si>
+  <si>
+    <t>Propeller guard</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005008709400103.html?spm=a2g0o.productlist.main.3.1fb94afcNT4R3V&amp;algo_pvid=0bc6315a-37e1-4019-b072-b9be3a0ff298&amp;algo_exp_id=0bc6315a-37e1-4019-b072-b9be3a0ff298-2&amp;pdp_ext_f=%7B%22order%22%3A%22111%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21CAD%2126.63%2110.05%21%21%21128.38%2148.45%21%402101f11417795914577768723e199e%2112000049464948114%21sea%21CA%216218818596%21X%211%210%21n_tag%3A-29919%3Bd%3A26a99932%3Bm03_new_user%3A-29895%3BpisId%3A5000000206825148&amp;curPageLogUid=58NwBPFRkHeL&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005008709400103%7C_p_origin_prod%3A</t>
   </si>
 </sst>
 </file>
@@ -102,10 +156,18 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -128,14 +190,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -468,10 +533,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2011A3C7-6E29-4B04-A4B3-8D5C6DD982D4}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
     <col min="2" max="2" width="17.6640625" customWidth="1"/>
     <col min="5" max="5" width="12.88671875" customWidth="1"/>
     <col min="6" max="6" width="12.109375" customWidth="1"/>
@@ -507,85 +572,166 @@
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
       <c r="C3">
         <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
       <c r="C4">
         <v>4</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
       <c r="C5">
         <v>4</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" s="1">
-        <v>48.29</v>
+        <v>27.99</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>1</v>
+      </c>
+      <c r="D7" s="1">
+        <v>10.050000000000001</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>1</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="C10">
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>17</v>
+      <c r="G11" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="https://www.pishop.ca/product/raspberry-pi-pico-non-wireless/?src=raspberrypi" xr:uid="{E324FA4C-B690-4CAF-8E81-D6E3C5F31062}"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://www.amazon.ca/sspa/click?ie=UTF8&amp;spc=MTo4MzQyNjM5OTI5OTUwMDk1OjE3Mjk3MDYyODc6c3BfYXRmOjIwMDAxMzE2NDkzMjQzMTo6MDo6&amp;url=%2FGikfun-MPU-6050-Accelerometer-Gyroscope-EK1091x3C%2Fdp%2FB07JPK26X2%2Fref%3Dsr_1_1_sspa%3Fcrid%3D2O4HWVBEJ20A4%26dib%3DeyJ2IjoiMSJ9.yGP5eUbdVmJDUTrIzbBfx6Z56aIHP2P0knsdlpoebBJeJQSxWPQ30tpGjc_6tszp-_ePdzDJfWVaW_JLG3k2ARWqXKHMsXeb-J1hYFKcEOdjUckig3UvOvo8ko6nwQNSk4fpyHayRlbplBTwaNg6cBo12_bxSaJkgUOg_tV3YlYgKfOelKlkhISPX86vIyyoGv5t_Aentx3yr8aFLHhTpdMtwDHbumXf4cemRmxFIiOQnoecChXjO21I8EzmVMie8shNdIuMR6_l9iGaLw-wZn5izkboOC_SSTSpgoQXdUo.NMjdZmbYoqKHMil81Unyb2pSn0X6sub1jXQ20r10o8Y%26dib_tag%3Dse%26keywords%3Dmpu6050%26qid%3D1729706287%26sprefix%3Dmpu6050%252Caps%252C109%26sr%3D8-1-spons%26sp_csd%3Dd2lkZ2V0TmFtZT1zcF9hdGY%26psc%3D1" xr:uid="{36DB5E99-E020-4FC0-A808-FDD38CC49911}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{3A04D775-44DC-49AA-99F1-B64603A6B9BF}"/>
+    <hyperlink ref="G6" r:id="rId4" xr:uid="{DB3B8138-12E4-48FE-A07E-DCEE2C15FCA8}"/>
+    <hyperlink ref="G13" r:id="rId5" display="https://www.amazon.ca/dp/B0CGRK4PZ9/ref=twister_B0DG61WS8R?_encoding=UTF8&amp;th=1" xr:uid="{3A41F495-7AE5-4D0B-8AD6-11984C57D661}"/>
+    <hyperlink ref="G8" r:id="rId6" display="https://www.amazon.ca/diymore-NRF24L01-Transceiver-Development-Compatible/dp/B0CGTWQ1BP/ref=sr_1_2?crid=N7UCP8G6BI4B&amp;dib=eyJ2IjoiMSJ9.QZWyUbxu-TTSXPtYa6jWsruNzInPMMFV3gyAWClyr16MjHZf7YNdMQIuLN8GSAJLMNuq_XRXSs0m0G5N2sjBIhiwK3Z4KvY9esEi6FYL8DDdseyeCPcQ7UDiiZB5kaqveZb2Wb01HFBp9DZ7mam3NE9XG7xw6UoxfQr9Gs2KcmLq1bCmSb6KFCsLg2RbVpZ_.s2cC8epe2nNatPfmenG33v9DyfE5sOt-iBPax3x-Jwg&amp;dib_tag=se&amp;keywords=nrf2401%2Bpa%2Blna&amp;qid=1729738278&amp;sprefix=nrf2401%2Bpa%2Blna%2Caps%2C100&amp;sr=8-2&amp;th=1" xr:uid="{32895D88-13E2-4EED-9DE0-D0F64222F8C9}"/>
+    <hyperlink ref="G9" r:id="rId7" display="https://www.amazon.ca/3300mAh-Battery-Helicopter-Airplane-Quadcopter/dp/B06XKQJZ8D/ref=sr_1_3_sspa?crid=25ULWJT7C7R66&amp;dib=eyJ2IjoiMSJ9.vYiAFw8wx-yRT8mrrvJ9F8iDFepM-goQbSaENXXv1p29dstKtQIYZaj1pn7rGGAGnxdMgoLHrOMQY91OKu51v8WLdjkq4eCi5EKe8z_K4cxcPbNP13Z1RKbgGnhs872aFBYGAh5eJIDjqL14oiAvwBw3eysdwf1lhxGnkO44qkwR113S583LExSDaa1urb2P0Y3cqxNoYUGVdBMDAMReQhU-SncWWSIWO4WEub3ZmS-SjueGbxuDC_AJcCAtAgLVxzIGmlzZL8pKUVzUuEKxSRbdivPCv_PMbDSxuVM6sK4.MMM72QgdE4MEe_CbP1cIRc1AZmN33Ov_NqM5hDzDp8A&amp;dib_tag=se&amp;keywords=4s+lipo+3000mah&amp;qid=1729985037&amp;sprefix=4S+LiPo+3%2Caps%2C81&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1" xr:uid="{797419C5-B3DF-4521-ADC8-9E9BBBE6FD40}"/>
+    <hyperlink ref="G5" r:id="rId8" xr:uid="{5940DDF6-F041-4847-BAD7-D80216FD9E60}"/>
+    <hyperlink ref="G14" r:id="rId9" display="https://www.amazon.ca/Leonardo-Headers-Compatible-Revision-Atmega32u4/dp/B00R237VGO/ref=sr_1_5?crid=MC17YS7O9GW9&amp;dib=eyJ2IjoiMSJ9.JMDO9D4vLSrBk_dqVlo-qYpD2emjzeRNG8QL6R8lWGXJUfLWeuU9lkv-AmMXoQJtSdgf6mjRUevYifaj76GKPczdq8-ZPujBm9azFK_jRVBBBxGQ1Iq-UgO_xESHbJL8yc7U0JgTmjihDuHQlgqb1gUqg-HUfgTJJeGmwypsadu_ivg6lFpJP9DrDnsP7rn8GIOX4dFpL6QSGQzulkHG-m7jKz6eSMoNHKHwlVnIjqLFz1WFLYKdxypg1TMg-ZzYmxVo8vHP00SBqcrwLuKwlAzuV_xVFZb3HXRtRz_V0YE.odwVut84lRl1xHouDFEbRF0YtTtdC_Kp_PjlXUqnVfU&amp;dib_tag=se&amp;keywords=arduino+leonardo&amp;qid=1730080008&amp;s=electronics&amp;sprefix=arduino+leonardo%2Celectronics%2C117&amp;sr=1-5" xr:uid="{1CE5D5D7-C23B-445D-9B4D-C372AC03A2BA}"/>
+    <hyperlink ref="G10" r:id="rId10" display="https://www.amazon.ca/Hobby-Fans-Professional-Balance-Discharger/dp/B09XC91BWJ/ref=sr_1_4_sspa?crid=38YSB72VYU6CH&amp;dib=eyJ2IjoiMSJ9.lnM2r6NhD8BJ0diYESu45Q1KQVNPU83hWGmkyM0idZS5APeLiSXCExN5IKIisgJh44yVmbwwP0E7zlbheFz3jKk_iwooFuWlrKiEnSXo5z2Hm1XyjvWMUTACgwu-K6noYPaE1KPmuIRgNc3VBkO0cb2wYWJEtMmLF4PDafVH0bSmUMwI1RbRu4_uRscwDZ7bZEq_wFA83RKeft44gD9qEySyDZEvFfr87CBL2GZFTJcoBO3JMDktAZ_sv86Svj0N_moTYnS4xrkUQI3MXR_SK9aKKv6LZfIlxSP2LDkF9Mw.o5z9RHJirvUDYHafc2uyBP8i3uW1x5a_-s5JsqYVZDc&amp;dib_tag=se&amp;keywords=lipo+battery+charger&amp;qid=1730085173&amp;sprefix=lipo+battery%2Caps%2C103&amp;sr=8-4-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1" xr:uid="{CD10D3CC-4A27-4ED6-8D18-60C1DAC9004B}"/>
+    <hyperlink ref="G11" r:id="rId11" display="https://www.aliexpress.com/item/32844447546.html?spm=a2g0o.productlist.main.3.4f2b2e3fBpldJr&amp;algo_pvid=b55a8f97-69bd-4069-bb1c-8dd3c90e7c96&amp;algo_exp_id=b55a8f97-69bd-4069-bb1c-8dd3c90e7c96-1&amp;pdp_npi=4%40dis%21CAD%2113.62%2112.91%21%21%219.61%219.11%21%402101e9a217299675201923501e356e%2166150463925%21sea%21CA%210%21ABX&amp;curPageLogUid=nGstg93h37eM&amp;utparam-url=scene%3Asearch%7Cquery_from%3A" xr:uid="{02565FF8-EDDF-4976-BCD6-25AA3303C5FF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>